--- a/data/trending_integrated_20261012_12.xlsx
+++ b/data/trending_integrated_20261012_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19830522780</v>
+        <v>19850356620</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131479795910</v>
+        <v>131521718000</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13700</v>
+        <v>13580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.98%</t>
+          <t>'+21.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>145106219305</v>
+        <v>146973198155</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자체 개발 특허 출원 소식에도 불구하고 외국인, 기관, 기타법인 매도세가 나타나며 주가 상승 동력에 대한 의문 제기.</t>
+          <t>금호건설, 외국인 대량 매도세 지속되며 주가 상승 동력 약화 전망. 금호전기 주가 흐름과 비교 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '외인 매도', '주가 전망']</t>
+          <t>['외국인 매도', '주가 흐름', '금호전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.72%</t>
+          <t>'+14.78%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10260396870</v>
+        <v>10310408897</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7800</v>
+        <v>7655</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.17%</t>
+          <t>'+8.12%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>88323350030</v>
+        <v>90570470275</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 입지 강조. 불황 속 226억 투자 및 반도체 수요 겨냥. 공매도 쇼퀴즈 및 국토부 승인 기대.</t>
+          <t>삼표시멘트, 불황 속 설비 투자 및 반도체 수요 겨냥. 공매도 관련 언급 및 지역 개발 사업 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설기초소재', '반도체 수요', '공매도 쇼퀴즈']</t>
+          <t>['설비 투자', '반도체 수요', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14790</v>
+        <v>14840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.33%</t>
+          <t>'+6.69%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F7" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G7" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>107120945385</v>
+        <v>111448983720</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산주 팔란티어 상승 및 우주 테마 언급과 함께 보호예수 해제 및 차익 실현 가능성에 대한 기대감과 우려 혼재.</t>
+          <t>덕산넵코어스, 미국 방산주 흐름과 연계된 기대감 속 보호예수 해제 및 차익실현 우려 공존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산 테마', '보호예수', '우주 테마']</t>
+          <t>['방산주', '보호예수 해제', '차익실현']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45200</v>
+        <v>45150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.99%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G8" t="n">
-        <v>2392</v>
+        <v>2463</v>
       </c>
       <c r="H8" t="n">
         <v>13.33</v>
@@ -1162,7 +1162,7 @@
         <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>32178343250</v>
+        <v>32421652500</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1222,13 +1222,13 @@
         <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H9" t="n">
         <v>1.48</v>
@@ -1254,7 +1254,7 @@
         <v>1.32</v>
       </c>
       <c r="O9" t="n">
-        <v>28943931337</v>
+        <v>29087748798</v>
       </c>
       <c r="P9" t="n">
         <v>2465</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255000</v>
+        <v>11020</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>484</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>1707</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>46.35</v>
+        <v>0.41</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>262000</v>
+        <v>11340</v>
       </c>
       <c r="K10" t="n">
-        <v>260000</v>
+        <v>11340</v>
       </c>
       <c r="L10" t="n">
-        <v>262500</v>
+        <v>12470</v>
       </c>
       <c r="M10" t="n">
-        <v>254000</v>
+        <v>10920</v>
       </c>
       <c r="N10" t="n">
-        <v>46.38</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1920329736500</v>
+        <v>27508959500</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>29750</v>
       </c>
       <c r="Q10" t="n">
-        <v>90200</v>
+        <v>10920</v>
       </c>
       <c r="R10" t="n">
-        <v>-416000</v>
+        <v>46000</v>
       </c>
       <c r="S10" t="n">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>역대급 실적 발표에도 주가 부양 실패 및 외국인 투자자 이탈에 대한 우려. 한국 증시 전반에 대한 부정적 전망.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '외국인 이탈']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1630000</v>
+        <v>254500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="G11" t="n">
-        <v>1765</v>
+        <v>1696</v>
       </c>
       <c r="H11" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K11" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L11" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M11" t="n">
-        <v>1605000</v>
+        <v>254000</v>
       </c>
       <c r="N11" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O11" t="n">
-        <v>2423255840500</v>
+        <v>2003211855750</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>-276000</v>
+        <v>-416000</v>
       </c>
       <c r="S11" t="n">
-        <v>14000</v>
+        <v>-81000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 하락과 자회사 솔리다임 중복 상장 논란에 대한 비판.</t>
+          <t>삼성전자, 역대급 실적에도 주가 부진 지속. 외국인 이탈 및 한국 증시 전반에 대한 비관론 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '중복 상장', '솔리다임']</t>
+          <t>['실적 발표', '외국인 이탈', '한국 증시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10980</v>
+        <v>1627000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>505</v>
       </c>
       <c r="G12" t="n">
-        <v>76</v>
+        <v>1794</v>
       </c>
       <c r="H12" t="n">
-        <v>0.41</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11340</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>11340</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>12470</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>10920</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.44</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>27330310160</v>
+        <v>2473109151000</v>
       </c>
       <c r="P12" t="n">
-        <v>29750</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>10920</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>46000</v>
+        <v>-276000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>SK하이닉스, 중복 상장 리스크 부각 및 정치적 이슈와 연계된 주가 하락 우려. 주주 가치 훼손 지적.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['중복 상장', '주주 가치', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18220</v>
+        <v>16130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>495</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>16670</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>16500</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>16870</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>16100</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>30682971510</v>
+        <v>40440169100</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>367000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LNG·FLNG 쌍끌이 수주 랠리 소식이 있으나, 국내 증시 전반의 하락세 및 타 조선주와의 비교 언급으로 불확실성 내포.</t>
+          <t>반복적인 '범죄 짓거리 멈추게 해야 합니다'와 '뱅크런' 관련 언급으로 부정적인 여론 형성. 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['LNG 수주', '조선주', '국내 증시']</t>
+          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16100</v>
+        <v>18220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>491</v>
+        <v>302</v>
       </c>
       <c r="H14" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16670</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>16500</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>16870</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>16100</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>39095753600</v>
+        <v>31218308355</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>367000</v>
+        <v>29000</v>
       </c>
       <c r="S14" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반복적인 '범죄 짓거리 멈추게 해야 합니다'와 '뱅크런' 관련 언급으로 부정적인 여론 형성. 명확한 근거 제시 부족.</t>
+          <t>삼성중공업, LNG·FLNG 수주 소식에도 주가 하락. 국내 증시 전반의 부진과 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
+          <t>['수주 랠리', '국내 증시', '정치 이슈']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7730</v>
+        <v>4060</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.27%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>-2.94</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>573</v>
+        <v>59</v>
       </c>
       <c r="H15" t="n">
-        <v>26.37</v>
+        <v>1.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8160</v>
+        <v>4270</v>
       </c>
       <c r="K15" t="n">
-        <v>8070</v>
+        <v>4150</v>
       </c>
       <c r="L15" t="n">
-        <v>8110</v>
+        <v>4495</v>
       </c>
       <c r="M15" t="n">
-        <v>7710</v>
+        <v>3940</v>
       </c>
       <c r="N15" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="O15" t="n">
-        <v>18204871740</v>
+        <v>17010820657</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q15" t="n">
-        <v>7710</v>
+        <v>2810</v>
       </c>
       <c r="R15" t="n">
-        <v>-595000</v>
+        <v>-92000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4030</v>
+        <v>7740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.62%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.94</v>
+        <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>56</v>
+        <v>585</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>26.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4270</v>
+        <v>8160</v>
       </c>
       <c r="K16" t="n">
-        <v>4150</v>
+        <v>8070</v>
       </c>
       <c r="L16" t="n">
-        <v>4495</v>
+        <v>8110</v>
       </c>
       <c r="M16" t="n">
-        <v>3940</v>
+        <v>7710</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>16790902052</v>
+        <v>18781324740</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>7710</v>
       </c>
       <c r="R16" t="n">
-        <v>-92000</v>
+        <v>-595000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15970</v>
+        <v>15940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.89%</t>
+          <t>'-6.07%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>66267790695</v>
+        <v>66829228905</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락 및 공매도 규제 관련 불만 제기. 광통신 시장 성장 전망.</t>
+          <t>대한광통신, 3분기 어닝 서프라이즈 및 광통신 테마 부각. 공매도 규제 및 기관 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '공매도 규제', '광통신']</t>
+          <t>['어닝 서프라이즈', '광통신 테마', '공매도 규제']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26100</v>
+        <v>26150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.12%</t>
+          <t>'-6.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>43258118900</v>
+        <v>43851231900</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_12.xlsx
+++ b/data/trending_integrated_20261012_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19850356620</v>
+        <v>19862659820</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131521718000</v>
+        <v>131598920180</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13580</v>
+        <v>13370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.90%</t>
+          <t>'+20.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>146973198155</v>
+        <v>150127140295</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설, 외국인 대량 매도세 지속되며 주가 상승 동력 약화 전망. 금호전기 주가 흐름과 비교 언급.</t>
+          <t>거래량 증가와 함께 상승했으나, 외인 매도세와 상승폭 제한에 대한 의견이 혼재됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인 매도', '주가 흐름', '금호전기']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.78%</t>
+          <t>'+14.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10310408897</v>
+        <v>10386373088</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7655</v>
+        <v>14920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.12%</t>
+          <t>'+7.26%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.1</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>418</v>
+        <v>248</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7080</v>
+        <v>13910</v>
       </c>
       <c r="K6" t="n">
-        <v>6830</v>
+        <v>13350</v>
       </c>
       <c r="L6" t="n">
-        <v>8100</v>
+        <v>15790</v>
       </c>
       <c r="M6" t="n">
-        <v>6720</v>
+        <v>13350</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>90570470275</v>
+        <v>113901903390</v>
       </c>
       <c r="P6" t="n">
-        <v>23500</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>2890</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>-136000</v>
+        <v>-3000</v>
       </c>
       <c r="S6" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼표시멘트, 불황 속 설비 투자 및 반도체 수요 겨냥. 공매도 관련 언급 및 지역 개발 사업 기대감.</t>
+          <t>덕산넵코어스, 미국 방산주 흐름과 연계된 기대감 속 보호예수 해제 및 차익실현 우려 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['설비 투자', '반도체 수요', '공매도']</t>
+          <t>['방산주', '보호예수 해제', '차익실현']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14840</v>
+        <v>7550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.69%</t>
+          <t>'+6.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>428</v>
       </c>
       <c r="H7" t="n">
-        <v>0.21</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13910</v>
+        <v>7080</v>
       </c>
       <c r="K7" t="n">
-        <v>13350</v>
+        <v>6830</v>
       </c>
       <c r="L7" t="n">
-        <v>15790</v>
+        <v>8100</v>
       </c>
       <c r="M7" t="n">
-        <v>13350</v>
+        <v>6720</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>111448983720</v>
+        <v>92971562995</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>23500</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>2890</v>
       </c>
       <c r="R7" t="n">
-        <v>-3000</v>
+        <v>-136000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 미국 방산주 흐름과 연계된 기대감 속 보호예수 해제 및 차익실현 우려 공존.</t>
+          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산주', '보호예수 해제', '차익실현']</t>
+          <t>['투자', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45150</v>
+        <v>45050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F8" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G8" t="n">
-        <v>2463</v>
+        <v>2516</v>
       </c>
       <c r="H8" t="n">
         <v>13.33</v>
@@ -1162,7 +1162,7 @@
         <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>32421652500</v>
+        <v>32641833850</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H9" t="n">
         <v>1.48</v>
@@ -1254,7 +1254,7 @@
         <v>1.32</v>
       </c>
       <c r="O9" t="n">
-        <v>29087748798</v>
+        <v>29287877808</v>
       </c>
       <c r="P9" t="n">
         <v>2465</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11020</v>
+        <v>254500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>487</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>1694</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41</v>
+        <v>46.35</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11340</v>
+        <v>262000</v>
       </c>
       <c r="K10" t="n">
-        <v>11340</v>
+        <v>260000</v>
       </c>
       <c r="L10" t="n">
-        <v>12470</v>
+        <v>262500</v>
       </c>
       <c r="M10" t="n">
-        <v>10920</v>
+        <v>253500</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>27508959500</v>
+        <v>2121093760000</v>
       </c>
       <c r="P10" t="n">
-        <v>29750</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>10920</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>46000</v>
+        <v>-416000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-81000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>역대급 실적 발표에도 불구하고 주가 부양 실패에 대한 비판과 한국 증시 침체에 대한 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['실적', '주가 부양']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254500</v>
+        <v>16160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>138</v>
       </c>
       <c r="F11" t="n">
-        <v>478</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>1696</v>
+        <v>520</v>
       </c>
       <c r="H11" t="n">
-        <v>46.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>262000</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>260000</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>262500</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>254000</v>
+        <v>16100</v>
       </c>
       <c r="N11" t="n">
-        <v>46.38</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>2003211855750</v>
+        <v>41402330975</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-416000</v>
+        <v>367000</v>
       </c>
       <c r="S11" t="n">
-        <v>-81000</v>
+        <v>17000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 역대급 실적에도 주가 부진 지속. 외국인 이탈 및 한국 증시 전반에 대한 비관론 제기.</t>
+          <t>반복적인 '범죄 짓거리 멈추게 해야 합니다'와 '뱅크런' 관련 언급으로 부정적인 여론 형성. 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인 이탈', '한국 증시']</t>
+          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1627000</v>
+        <v>18280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
-        <v>505</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>1794</v>
+        <v>308</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>18100</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O12" t="n">
-        <v>2473109151000</v>
+        <v>32610797575</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>18100</v>
       </c>
       <c r="R12" t="n">
-        <v>-276000</v>
+        <v>29000</v>
       </c>
       <c r="S12" t="n">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SK하이닉스, 중복 상장 리스크 부각 및 정치적 이슈와 연계된 주가 하락 우려. 주주 가치 훼손 지적.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['중복 상장', '주주 가치', '정치적 이슈']</t>
+          <t>['수주', 'LNG']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16130</v>
+        <v>1624000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>136</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>519</v>
       </c>
       <c r="G13" t="n">
-        <v>495</v>
+        <v>1818</v>
       </c>
       <c r="H13" t="n">
-        <v>9.470000000000001</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16670</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>16500</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>16870</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>16100</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>9.460000000000001</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>40440169100</v>
+        <v>2527841058500</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>367000</v>
+        <v>-276000</v>
       </c>
       <c r="S13" t="n">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반복적인 '범죄 짓거리 멈추게 해야 합니다'와 '뱅크런' 관련 언급으로 부정적인 여론 형성. 명확한 근거 제시 부족.</t>
+          <t>자회사 상장 및 주가 하락에 대한 불만이 고조되며, 정치적 요인에 따른 시장 침체 우려도 제기됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
+          <t>['상장', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18220</v>
+        <v>10870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-4.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61</v>
+        <v>0.41</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18860</v>
+        <v>11340</v>
       </c>
       <c r="K14" t="n">
-        <v>18690</v>
+        <v>11340</v>
       </c>
       <c r="L14" t="n">
-        <v>18760</v>
+        <v>12470</v>
       </c>
       <c r="M14" t="n">
-        <v>18100</v>
+        <v>10810</v>
       </c>
       <c r="N14" t="n">
-        <v>27.68</v>
+        <v>0.44</v>
       </c>
       <c r="O14" t="n">
-        <v>31218308355</v>
+        <v>28030680770</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>29750</v>
       </c>
       <c r="Q14" t="n">
-        <v>18100</v>
+        <v>10810</v>
       </c>
       <c r="R14" t="n">
-        <v>29000</v>
+        <v>46000</v>
       </c>
       <c r="S14" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성중공업, LNG·FLNG 수주 소식에도 주가 하락. 국내 증시 전반의 부진과 정치적 이슈 언급.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주 랠리', '국내 증시', '정치 이슈']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4060</v>
+        <v>7740</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2.94</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>598</v>
       </c>
       <c r="H15" t="n">
-        <v>1.52</v>
+        <v>26.37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4270</v>
+        <v>8160</v>
       </c>
       <c r="K15" t="n">
-        <v>4150</v>
+        <v>8070</v>
       </c>
       <c r="L15" t="n">
-        <v>4495</v>
+        <v>8110</v>
       </c>
       <c r="M15" t="n">
-        <v>3940</v>
+        <v>7710</v>
       </c>
       <c r="N15" t="n">
-        <v>4.46</v>
+        <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>17010820657</v>
+        <v>19202624895</v>
       </c>
       <c r="P15" t="n">
-        <v>5470</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>2810</v>
+        <v>7710</v>
       </c>
       <c r="R15" t="n">
-        <v>-92000</v>
+        <v>-595000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>주가 회복 불능 및 투자 동기에 대한 의문이 제기되며, 유상증자 및 상폐 가능성에 대한 부정적 전망이 우세함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['유상증자', '상폐']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7740</v>
+        <v>4040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.01</v>
+        <v>-2.94</v>
       </c>
       <c r="E16" t="n">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>585</v>
+        <v>62</v>
       </c>
       <c r="H16" t="n">
-        <v>26.37</v>
+        <v>1.52</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8160</v>
+        <v>4270</v>
       </c>
       <c r="K16" t="n">
-        <v>8070</v>
+        <v>4150</v>
       </c>
       <c r="L16" t="n">
-        <v>8110</v>
+        <v>4495</v>
       </c>
       <c r="M16" t="n">
-        <v>7710</v>
+        <v>3940</v>
       </c>
       <c r="N16" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>18781324740</v>
+        <v>17090168622</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q16" t="n">
-        <v>7710</v>
+        <v>2810</v>
       </c>
       <c r="R16" t="n">
-        <v>-595000</v>
+        <v>-92000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15940</v>
+        <v>15890</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.07%</t>
+          <t>'-6.36%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>66829228905</v>
+        <v>67730068600</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26150</v>
+        <v>26000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.94%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2076,13 +2076,13 @@
         <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>26050</v>
+        <v>26000</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>43851231900</v>
+        <v>45331955400</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_12.xlsx
+++ b/data/trending_integrated_20261012_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19862659820</v>
+        <v>19874300540</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131598920180</v>
+        <v>131667177800</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13370</v>
+        <v>13410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.02%</t>
+          <t>'+20.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>150127140295</v>
+        <v>152311512120</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1586</v>
+        <v>1575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.35%</t>
+          <t>'+13.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10386373088</v>
+        <v>10444363434</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14920</v>
+        <v>7550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.26%</t>
+          <t>'+6.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>248</v>
+        <v>432</v>
       </c>
       <c r="H6" t="n">
-        <v>0.21</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13910</v>
+        <v>7080</v>
       </c>
       <c r="K6" t="n">
-        <v>13350</v>
+        <v>6830</v>
       </c>
       <c r="L6" t="n">
-        <v>15790</v>
+        <v>8100</v>
       </c>
       <c r="M6" t="n">
-        <v>13350</v>
+        <v>6720</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>113901903390</v>
+        <v>95481737405</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>23500</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>-3000</v>
+        <v>-136000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 미국 방산주 흐름과 연계된 기대감 속 보호예수 해제 및 차익실현 우려 공존.</t>
+          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['방산주', '보호예수 해제', '차익실현']</t>
+          <t>['투자', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7550</v>
+        <v>14770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.64%</t>
+          <t>'+6.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.1</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G7" t="n">
-        <v>428</v>
+        <v>273</v>
       </c>
       <c r="H7" t="n">
-        <v>1.99</v>
+        <v>0.21</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7080</v>
+        <v>13910</v>
       </c>
       <c r="K7" t="n">
-        <v>6830</v>
+        <v>13350</v>
       </c>
       <c r="L7" t="n">
-        <v>8100</v>
+        <v>15790</v>
       </c>
       <c r="M7" t="n">
-        <v>6720</v>
+        <v>13350</v>
       </c>
       <c r="N7" t="n">
-        <v>3.09</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>92971562995</v>
+        <v>117108339280</v>
       </c>
       <c r="P7" t="n">
-        <v>23500</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>2890</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-136000</v>
+        <v>-3000</v>
       </c>
       <c r="S7" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
+          <t>미국 방산주 상승에 따른 테마 기대감과 함께, 보호예수 해제 및 주가 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자', '공매도']</t>
+          <t>['방산 테마', '보호예수', '주가 변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45050</v>
+        <v>45150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G8" t="n">
-        <v>2516</v>
+        <v>2527</v>
       </c>
       <c r="H8" t="n">
         <v>13.33</v>
@@ -1162,7 +1162,7 @@
         <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>32641833850</v>
+        <v>32849239100</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 리보세라닙 관련 FDA 재승인 서류 제출 공시 확인. 연말 30만 기대감 및 공매도 세력에 대한 비판.</t>
+          <t>HLB 간암 1차 치료제 리보세라닙 관련 FDA 재승인 서류 제출 공시 확인 및 연말 목표 주가 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 재승인', '리보세라닙', '공매도']</t>
+          <t>['FDA 재승인', '리보세라닙', '공시']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H9" t="n">
         <v>1.48</v>
@@ -1254,7 +1254,7 @@
         <v>1.32</v>
       </c>
       <c r="O9" t="n">
-        <v>29287877808</v>
+        <v>29397865413</v>
       </c>
       <c r="P9" t="n">
         <v>2465</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254500</v>
+        <v>11080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-2.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>487</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1694</v>
+        <v>80</v>
       </c>
       <c r="H10" t="n">
-        <v>46.35</v>
+        <v>0.41</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>262000</v>
+        <v>11340</v>
       </c>
       <c r="K10" t="n">
-        <v>260000</v>
+        <v>11340</v>
       </c>
       <c r="L10" t="n">
-        <v>262500</v>
+        <v>12470</v>
       </c>
       <c r="M10" t="n">
-        <v>253500</v>
+        <v>10810</v>
       </c>
       <c r="N10" t="n">
-        <v>46.38</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>2121093760000</v>
+        <v>28508695510</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>29750</v>
       </c>
       <c r="Q10" t="n">
-        <v>90200</v>
+        <v>10810</v>
       </c>
       <c r="R10" t="n">
-        <v>-416000</v>
+        <v>46000</v>
       </c>
       <c r="S10" t="n">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>역대급 실적 발표에도 불구하고 주가 부양 실패에 대한 비판과 한국 증시 침체에 대한 우려가 제기됨.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '주가 부양']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16160</v>
+        <v>254500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>138</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>491</v>
       </c>
       <c r="G11" t="n">
-        <v>520</v>
+        <v>1778</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>46.35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>262000</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>260000</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>262500</v>
       </c>
       <c r="M11" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>46.38</v>
       </c>
       <c r="O11" t="n">
-        <v>41402330975</v>
+        <v>2166642098250</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>367000</v>
+        <v>-416000</v>
       </c>
       <c r="S11" t="n">
-        <v>17000</v>
+        <v>-81000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반복적인 '범죄 짓거리 멈추게 해야 합니다'와 '뱅크런' 관련 언급으로 부정적인 여론 형성. 명확한 근거 제시 부족.</t>
+          <t>영업이익 대비 주가 부진에 대한 정치적 원인 분석 및 향후 주가 하락 전망. 외국인 이탈 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
+          <t>['영업이익', '주가 부진', '외국인 이탈']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18280</v>
+        <v>16180</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>308</v>
+        <v>545</v>
       </c>
       <c r="H12" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18860</v>
+        <v>16670</v>
       </c>
       <c r="K12" t="n">
-        <v>18690</v>
+        <v>16500</v>
       </c>
       <c r="L12" t="n">
-        <v>18760</v>
+        <v>16870</v>
       </c>
       <c r="M12" t="n">
-        <v>18100</v>
+        <v>16100</v>
       </c>
       <c r="N12" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>32610797575</v>
+        <v>42292098765</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>18100</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>29000</v>
+        <v>367000</v>
       </c>
       <c r="S12" t="n">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
+          <t>대차 거래 해지 및 뱅크런 관련 주장과 함께, 주주 행동 촉구 및 정치적 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', 'LNG']</t>
+          <t>['대차 거래', '뱅크런', '주주 연대']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1624000</v>
+        <v>18270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>519</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>1818</v>
+        <v>309</v>
       </c>
       <c r="H13" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K13" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L13" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M13" t="n">
-        <v>1605000</v>
+        <v>18100</v>
       </c>
       <c r="N13" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2527841058500</v>
+        <v>33234477845</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>18100</v>
       </c>
       <c r="R13" t="n">
-        <v>-276000</v>
+        <v>29000</v>
       </c>
       <c r="S13" t="n">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자회사 상장 및 주가 하락에 대한 불만이 고조되며, 정치적 요인에 따른 시장 침체 우려도 제기됨.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상장', '주가 하락']</t>
+          <t>['수주', 'LNG']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,99 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10870</v>
+        <v>1626000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.14%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>515</v>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
+        <v>1774</v>
       </c>
       <c r="H14" t="n">
-        <v>0.41</v>
+        <v>49.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11340</v>
+        <v>1681000</v>
       </c>
       <c r="K14" t="n">
-        <v>11340</v>
+        <v>1640000</v>
       </c>
       <c r="L14" t="n">
-        <v>12470</v>
+        <v>1653000</v>
       </c>
       <c r="M14" t="n">
-        <v>10810</v>
+        <v>1605000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>49.59</v>
       </c>
       <c r="O14" t="n">
-        <v>28030680770</v>
+        <v>2580946957000</v>
       </c>
       <c r="P14" t="n">
-        <v>29750</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>10810</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>46000</v>
+        <v>-276000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>정치적 요인 및 자회사 상장 관련 논란으로 인한 주가 하락 및 주주 가치 훼손 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['정치적 요인', '자회사 상장', '주주 가치 훼손']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F15" t="n">
         <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>598</v>
+        <v>644</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>19202624895</v>
+        <v>19890759645</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 회복 불능 및 투자 동기에 대한 의문이 제기되며, 유상증자 및 상폐 가능성에 대한 부정적 전망이 우세함.</t>
+          <t>삼성디스플레이 기업 가치 대비 주가 저평가 및 투자 심리 악화. 기술 및 유상증자 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유상증자', '상폐']</t>
+          <t>['기업 가치', '주가 저평가', '유상증자']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4040</v>
+        <v>4005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-6.21%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-2.94</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H16" t="n">
         <v>1.52</v>
@@ -1898,7 +1898,7 @@
         <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>17090168622</v>
+        <v>17185583867</v>
       </c>
       <c r="P16" t="n">
         <v>5470</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15890</v>
+        <v>15860</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.36%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>67730068600</v>
+        <v>68724330160</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26000</v>
+        <v>26050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.47%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>45331955400</v>
+        <v>46259382300</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_12.xlsx
+++ b/data/trending_integrated_20261012_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19874300540</v>
+        <v>19897338620</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131667177800</v>
+        <v>131754885410</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13410</v>
+        <v>13490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.38%</t>
+          <t>'+21.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>152311512120</v>
+        <v>154473251240</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -854,13 +854,13 @@
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10444363434</v>
+        <v>10560025364</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7550</v>
+        <v>15210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.64%</t>
+          <t>'+9.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.1</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>432</v>
+        <v>285</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7080</v>
+        <v>13910</v>
       </c>
       <c r="K6" t="n">
-        <v>6830</v>
+        <v>13350</v>
       </c>
       <c r="L6" t="n">
-        <v>8100</v>
+        <v>15790</v>
       </c>
       <c r="M6" t="n">
-        <v>6720</v>
+        <v>13350</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>95481737405</v>
+        <v>123071649525</v>
       </c>
       <c r="P6" t="n">
-        <v>23500</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>2890</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>-136000</v>
+        <v>-3000</v>
       </c>
       <c r="S6" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
+          <t>보호예수 해제 및 방산·우주 테마 언급. 단기 변동성 주의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['투자', '공매도']</t>
+          <t>['보호예수', '방산테마', '우주테마']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14770</v>
+        <v>7510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.18%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>273</v>
+        <v>458</v>
       </c>
       <c r="H7" t="n">
-        <v>0.21</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13910</v>
+        <v>7080</v>
       </c>
       <c r="K7" t="n">
-        <v>13350</v>
+        <v>6830</v>
       </c>
       <c r="L7" t="n">
-        <v>15790</v>
+        <v>8100</v>
       </c>
       <c r="M7" t="n">
-        <v>13350</v>
+        <v>6720</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>117108339280</v>
+        <v>96853363060</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>23500</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>2890</v>
       </c>
       <c r="R7" t="n">
-        <v>-3000</v>
+        <v>-136000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산주 상승에 따른 테마 기대감과 함께, 보호예수 해제 및 주가 변동성에 대한 언급.</t>
+          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산 테마', '보호예수', '주가 변동성']</t>
+          <t>['투자', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45150</v>
+        <v>45300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G8" t="n">
-        <v>2527</v>
+        <v>2561</v>
       </c>
       <c r="H8" t="n">
         <v>13.33</v>
@@ -1162,7 +1162,7 @@
         <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>32849239100</v>
+        <v>33276946350</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 리보세라닙 관련 FDA 재승인 서류 제출 공시 확인 및 연말 목표 주가 기대.</t>
+          <t>FDA 간암 1차 치료제 리보세라닙 재승인 서류 제출 공시 확인. 연말 30만 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 재승인', '리보세라닙', '공시']</t>
+          <t>['FDA', '리보세라닙', '재신청']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2255</v>
+        <v>11190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-1.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="H9" t="n">
-        <v>1.48</v>
+        <v>0.41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2305</v>
+        <v>11340</v>
       </c>
       <c r="K9" t="n">
-        <v>2430</v>
+        <v>11340</v>
       </c>
       <c r="L9" t="n">
-        <v>2445</v>
+        <v>12470</v>
       </c>
       <c r="M9" t="n">
-        <v>2210</v>
+        <v>10810</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>29397865413</v>
+        <v>28687171670</v>
       </c>
       <c r="P9" t="n">
-        <v>2465</v>
+        <v>29750</v>
       </c>
       <c r="Q9" t="n">
-        <v>865</v>
+        <v>10810</v>
       </c>
       <c r="R9" t="n">
-        <v>-442000</v>
+        <v>46000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11080</v>
+        <v>18285</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="H10" t="n">
-        <v>0.41</v>
+        <v>27.61</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11340</v>
+        <v>18860</v>
       </c>
       <c r="K10" t="n">
-        <v>11340</v>
+        <v>18690</v>
       </c>
       <c r="L10" t="n">
-        <v>12470</v>
+        <v>18760</v>
       </c>
       <c r="M10" t="n">
-        <v>10810</v>
+        <v>18100</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>27.68</v>
       </c>
       <c r="O10" t="n">
-        <v>28508695510</v>
+        <v>33833546810</v>
       </c>
       <c r="P10" t="n">
-        <v>29750</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>10810</v>
+        <v>18100</v>
       </c>
       <c r="R10" t="n">
-        <v>46000</v>
+        <v>29000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['수주', 'LNG']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254500</v>
+        <v>16150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>146</v>
       </c>
       <c r="F11" t="n">
-        <v>491</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>1778</v>
+        <v>614</v>
       </c>
       <c r="H11" t="n">
-        <v>46.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>262000</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>260000</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>262500</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>253500</v>
+        <v>16100</v>
       </c>
       <c r="N11" t="n">
-        <v>46.38</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>2166642098250</v>
+        <v>43489625580</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-416000</v>
+        <v>367000</v>
       </c>
       <c r="S11" t="n">
-        <v>-81000</v>
+        <v>17000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>영업이익 대비 주가 부진에 대한 정치적 원인 분석 및 향후 주가 하락 전망. 외국인 이탈 우려.</t>
+          <t>대차거래 및 뱅크런 관련 의혹 제기. 소액주주연대 활동 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부진', '외국인 이탈']</t>
+          <t>['대차거래', '뱅크런', '소액주주연대']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16180</v>
+        <v>253750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>493</v>
       </c>
       <c r="G12" t="n">
-        <v>545</v>
+        <v>1774</v>
       </c>
       <c r="H12" t="n">
-        <v>9.470000000000001</v>
+        <v>46.35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16670</v>
+        <v>262000</v>
       </c>
       <c r="K12" t="n">
-        <v>16500</v>
+        <v>260000</v>
       </c>
       <c r="L12" t="n">
-        <v>16870</v>
+        <v>262500</v>
       </c>
       <c r="M12" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="N12" t="n">
-        <v>9.460000000000001</v>
+        <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>42292098765</v>
+        <v>2220410132000</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>367000</v>
+        <v>-416000</v>
       </c>
       <c r="S12" t="n">
-        <v>17000</v>
+        <v>-81000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차 거래 해지 및 뱅크런 관련 주장과 함께, 주주 행동 촉구 및 정치적 언급.</t>
+          <t>정치적 요인과 정부 정책에 따른 주가 하락 우려. 역대급 실적에도 주가 부양 실패 가능성 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차 거래', '뱅크런', '주주 연대']</t>
+          <t>['영업이익', '주가부양', '정부정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18270</v>
+        <v>1621000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>519</v>
       </c>
       <c r="G13" t="n">
-        <v>309</v>
+        <v>1822</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>33234477845</v>
+        <v>2636328637500</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>-276000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
+          <t>정치적 요인 및 정부 정책 관련 주가 하락 우려. 자회사 상장 논란.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', 'LNG']</t>
+          <t>['정치적요인', '자회사상장', '주가하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,99 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1626000</v>
+        <v>2220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>1774</v>
+        <v>122</v>
       </c>
       <c r="H14" t="n">
-        <v>49.52</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1681000</v>
+        <v>2305</v>
       </c>
       <c r="K14" t="n">
-        <v>1640000</v>
+        <v>2430</v>
       </c>
       <c r="L14" t="n">
-        <v>1653000</v>
+        <v>2445</v>
       </c>
       <c r="M14" t="n">
-        <v>1605000</v>
+        <v>2210</v>
       </c>
       <c r="N14" t="n">
-        <v>49.59</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>2580946957000</v>
+        <v>29620811113</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>2465</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>-276000</v>
+        <v>-442000</v>
       </c>
       <c r="S14" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 요인 및 자회사 상장 관련 논란으로 인한 주가 하락 및 주주 가치 훼손 우려.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치적 요인', '자회사 상장', '주주 가치 훼손']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7740</v>
+        <v>7730</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>19890759645</v>
+        <v>20580104310</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1851,184 +1851,184 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4005</v>
+        <v>15840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.21%</t>
+          <t>'-6.66%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.94</v>
+        <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>63</v>
+        <v>452</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4270</v>
+        <v>16970</v>
       </c>
       <c r="K16" t="n">
-        <v>4150</v>
+        <v>17030</v>
       </c>
       <c r="L16" t="n">
-        <v>4495</v>
+        <v>17400</v>
       </c>
       <c r="M16" t="n">
-        <v>3940</v>
+        <v>15650</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>17185583867</v>
+        <v>70082214405</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-92000</v>
+        <v>59000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>3분기 실적 어닝 서프라이즈 확인. 광통신 시장 성장 및 AI 테마 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['실적', '어닝서프라이즈', '광통신']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15860</v>
+        <v>3980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.6</v>
+        <v>-2.94</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>443</v>
+        <v>67</v>
       </c>
       <c r="H17" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16970</v>
+        <v>4270</v>
       </c>
       <c r="K17" t="n">
-        <v>17030</v>
+        <v>4150</v>
       </c>
       <c r="L17" t="n">
-        <v>17400</v>
+        <v>4495</v>
       </c>
       <c r="M17" t="n">
-        <v>15650</v>
+        <v>3940</v>
       </c>
       <c r="N17" t="n">
-        <v>3.97</v>
+        <v>4.46</v>
       </c>
       <c r="O17" t="n">
-        <v>68724330160</v>
+        <v>17396775057</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>5470</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>2810</v>
       </c>
       <c r="R17" t="n">
-        <v>59000</v>
+        <v>-92000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대한광통신, 3분기 어닝 서프라이즈 및 광통신 테마 부각. 공매도 규제 및 기관 매수세 유입 기대.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광통신 테마', '공매도 규제']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26050</v>
+        <v>26000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>46259382300</v>
+        <v>47156323400</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_12.xlsx
+++ b/data/trending_integrated_20261012_12.xlsx
@@ -584,7 +584,7 @@
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19897338620</v>
+        <v>19904463660</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131754885410</v>
+        <v>131806759430</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13490</v>
+        <v>13460</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.10%</t>
+          <t>'+20.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
         <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>154473251240</v>
+        <v>156137344195</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.55%</t>
+          <t>'+14.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10560025364</v>
+        <v>10628197098</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15210</v>
+        <v>15390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.35%</t>
+          <t>'+10.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G6" t="n">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="H6" t="n">
         <v>0.21</v>
@@ -978,7 +978,7 @@
         <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>123071649525</v>
+        <v>131057276520</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 방산·우주 테마 언급. 단기 변동성 주의.</t>
+          <t>방산 및 우주 테마 기대감 속 주가 상승. 누리호 발사 성공 관련 긍정적 모멘텀.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보호예수', '방산테마', '우주테마']</t>
+          <t>['방산', '우주', '누리호']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7510</v>
+        <v>7580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="H7" t="n">
         <v>1.99</v>
@@ -1070,7 +1070,7 @@
         <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>96853363060</v>
+        <v>98210923425</v>
       </c>
       <c r="P7" t="n">
         <v>23500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 반도체 수요 겨냥 투자 소식과 함께 공매도 관련 언급 및 상승에 대한 기대감이 나타남.</t>
+          <t>성수 메가프로젝트 관련 건설 기초 소재 사업 기대감. 반도체 수요 겨냥 투자 소식.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['투자', '공매도']</t>
+          <t>['건설', '투자', '반도체']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45300</v>
+        <v>44950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.77%</t>
+          <t>'-1.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F8" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G8" t="n">
-        <v>2561</v>
+        <v>2592</v>
       </c>
       <c r="H8" t="n">
         <v>13.33</v>
@@ -1162,7 +1162,7 @@
         <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>33276946350</v>
+        <v>33705432125</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11190</v>
+        <v>11130</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.32%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="n">
         <v>0.41</v>
@@ -1254,7 +1254,7 @@
         <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>28687171670</v>
+        <v>28837310405</v>
       </c>
       <c r="P9" t="n">
         <v>29750</v>
@@ -1299,123 +1299,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18285</v>
+        <v>2240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>309</v>
+        <v>123</v>
       </c>
       <c r="H10" t="n">
-        <v>27.61</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18860</v>
+        <v>2305</v>
       </c>
       <c r="K10" t="n">
-        <v>18690</v>
+        <v>2430</v>
       </c>
       <c r="L10" t="n">
-        <v>18760</v>
+        <v>2445</v>
       </c>
       <c r="M10" t="n">
-        <v>18100</v>
+        <v>2210</v>
       </c>
       <c r="N10" t="n">
-        <v>27.68</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>33833546810</v>
+        <v>29695282353</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>2465</v>
       </c>
       <c r="Q10" t="n">
-        <v>18100</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>29000</v>
+        <v>-442000</v>
       </c>
       <c r="S10" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 시장 불안정성에 대한 우려가 나타남.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주', 'LNG']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16150</v>
+        <v>18220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>614</v>
+        <v>316</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>18860</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>18690</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>18760</v>
       </c>
       <c r="M11" t="n">
-        <v>16100</v>
+        <v>18100</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="O11" t="n">
-        <v>43489625580</v>
+        <v>34357580795</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>18100</v>
       </c>
       <c r="R11" t="n">
-        <v>367000</v>
+        <v>29000</v>
       </c>
       <c r="S11" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차거래 및 뱅크런 관련 의혹 제기. 소액주주연대 활동 언급.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 지속. 정치 및 외교적 요인으로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차거래', '뱅크런', '소액주주연대']</t>
+          <t>['수주', '주가하락', '정치']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253750</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="G12" t="n">
-        <v>1774</v>
+        <v>1730</v>
       </c>
       <c r="H12" t="n">
         <v>46.35</v>
@@ -1524,13 +1524,13 @@
         <v>262500</v>
       </c>
       <c r="M12" t="n">
-        <v>253500</v>
+        <v>252500</v>
       </c>
       <c r="N12" t="n">
         <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2220410132000</v>
+        <v>2340830834250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 요인과 정부 정책에 따른 주가 하락 우려. 역대급 실적에도 주가 부양 실패 가능성 제기.</t>
+          <t>정치적 이슈와 정부 정책에 대한 불만으로 인한 주가 하락 우려. 일부 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가부양', '정부정책']</t>
+          <t>['정치', '정부정책', '주가하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1621000</v>
+        <v>1615000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.57%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G13" t="n">
-        <v>1822</v>
+        <v>1849</v>
       </c>
       <c r="H13" t="n">
         <v>49.52</v>
@@ -1622,7 +1622,7 @@
         <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>2636328637500</v>
+        <v>2741558016500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 요인 및 정부 정책 관련 주가 하락 우려. 자회사 상장 논란.</t>
+          <t>정치적 이슈와 자회사 상장 관련 논란으로 인한 주가 하락 우려. 투자자 불만 고조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치적요인', '자회사상장', '주가하락']</t>
+          <t>['정치', '자회사상장', '주가하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,123 +1667,123 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2220</v>
+        <v>7710</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="G14" t="n">
-        <v>122</v>
+        <v>672</v>
       </c>
       <c r="H14" t="n">
-        <v>1.48</v>
+        <v>26.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2305</v>
+        <v>8160</v>
       </c>
       <c r="K14" t="n">
-        <v>2430</v>
+        <v>8070</v>
       </c>
       <c r="L14" t="n">
-        <v>2445</v>
+        <v>8110</v>
       </c>
       <c r="M14" t="n">
-        <v>2210</v>
+        <v>7710</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>26.38</v>
       </c>
       <c r="O14" t="n">
-        <v>29620811113</v>
+        <v>21459226035</v>
       </c>
       <c r="P14" t="n">
-        <v>2465</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>865</v>
+        <v>7710</v>
       </c>
       <c r="R14" t="n">
-        <v>-442000</v>
+        <v>-595000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>삼성디스플레이 기업 가치 대비 주가 저평가 및 투자 심리 악화. 기술 및 유상증자 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['기업 가치', '주가 저평가', '유상증자']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7730</v>
+        <v>16120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.27%</t>
+          <t>'-6.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>657</v>
+        <v>638</v>
       </c>
       <c r="H15" t="n">
-        <v>26.37</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8160</v>
+        <v>17220</v>
       </c>
       <c r="K15" t="n">
-        <v>8070</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8110</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7710</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26.38</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>20580104310</v>
+        <v>44323000000</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7710</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-595000</v>
+        <v>367000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성디스플레이 기업 가치 대비 주가 저평가 및 투자 심리 악화. 기술 및 유상증자 관련 부정적 전망.</t>
+          <t>대차 해지와 뱅크런 관련 우려 제기. 소액주주 운동 및 범죄 행위 중단 촉구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기업 가치', '주가 저평가', '유상증자']</t>
+          <t>['대차', '뱅크런', '소액주주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15840</v>
+        <v>15790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.66%</t>
+          <t>'-6.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F16" t="n">
         <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H16" t="n">
         <v>3.37</v>
@@ -1898,7 +1898,7 @@
         <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>70082214405</v>
+        <v>71681628830</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 실적 어닝 서프라이즈 확인. 광통신 시장 성장 및 AI 테마 기대감.</t>
+          <t>AI 및 광통신 테마 성장 기대감. 3분기 어닝 서프라이즈 기록.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '어닝서프라이즈', '광통신']</t>
+          <t>['AI', '광통신', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3980</v>
+        <v>3940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.79%</t>
+          <t>'-7.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.94</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
         <v>67</v>
@@ -1984,13 +1984,13 @@
         <v>4495</v>
       </c>
       <c r="M17" t="n">
-        <v>3940</v>
+        <v>3935</v>
       </c>
       <c r="N17" t="n">
         <v>4.46</v>
       </c>
       <c r="O17" t="n">
-        <v>17396775057</v>
+        <v>17576233772</v>
       </c>
       <c r="P17" t="n">
         <v>5470</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.47%</t>
+          <t>'-7.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2076,13 +2076,13 @@
         <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>47156323400</v>
+        <v>48707169150</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
